--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -1,106 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ConditionExpression" sheetId="1" r:id="rId1"/>
+    <sheet name="ConditionExpression" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>ConditionExpression</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>b577b9def34b94cf</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>stable_key</t>
-  </si>
-  <si>
-    <t>node</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>union&lt;ConditionExpressionNode&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>key;range=1..2147483647</t>
-  </si>
-  <si>
-    <t>length=1..160</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -119,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -413,112 +407,191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ConditionExpression</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>b577b9def34b94cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>node</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>node</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>union&lt;ConditionExpressionNode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>length=1..160</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>22</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>standard-v1.condition.always</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,21 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>24201</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>probe.clara.condition.true</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,6 +609,36 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980551</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.condition.always</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>980552</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.condition.no-branches</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":980406,"minimum_count":0,"maximum_count":0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,6 +639,36 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>990551</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.condition.always</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>990552</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.condition.current-subject-unshielded</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":991102,"comparison":"Equal","right_expression_id":991103}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,6 +669,36 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1000551</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.condition.always</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1000552</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.condition.direwolf-coordinated</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1001108,"comparison":"Greater","right_expression_id":1001109}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,6 +699,51 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1010551</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.condition.always</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1010552</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.condition.reset-sequence</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1011108,"comparison":"Greater","right_expression_id":1011107}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1010553</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.condition.needs-absorption</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1011109,"comparison":"Greater","right_expression_id":1011107}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,6 +744,81 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.always</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1020562</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.core-wind</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020503}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1020563</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.core-lightning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020504}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1020564</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.core-imaginary</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020505}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020565</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.no-flying-swords</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1020411,"minimum_count":0,"maximum_count":0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,6 +819,36 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1030561</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.condition.always</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1030562</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.condition.adjacent-frozen</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1030411,"minimum_count":1,"maximum_count":2}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -849,6 +849,51 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1040561</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.condition.always</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1040562</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.condition.shielded</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1041103,"comparison":"Greater","right_expression_id":1041105}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1040563</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.condition.unshielded</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1041103,"comparison":"Equal","right_expression_id":1041105}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,36 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1050551</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.condition.always</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1050552</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.condition.reset</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1051108,"comparison":"Greater","right_expression_id":1051107}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,246 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.always</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1060552</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.sunset-ready</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1061117,"comparison":"GreaterOrEqual","right_expression_id":1061111}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060553</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.nightfall-second</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1061118,"comparison":"GreaterOrEqual","right_expression_id":1061111}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1060554</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.tomb-last</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1061119,"comparison":"LessOrEqual","right_expression_id":1061110}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1060555</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.tomb-more</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1061119,"comparison":"Greater","right_expression_id":1061110}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1060556</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.no-dreams</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060407,"minimum_count":0,"maximum_count":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1060557</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.sunset-not-ready</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{"type":"Not","condition_id":1060552}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1060558</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.nightfall-not-second</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{"type":"Not","condition_id":1060553}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1060560</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.primary-formation-0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060410,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1060561</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.primary-formation-1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060411,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1060562</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.primary-formation-2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060412,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1060563</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.primary-formation-3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060413,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1060570</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.current-formation-0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060420,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1060571</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.current-formation-1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060421,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1060572</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.current-formation-2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060422,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1060573</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.current-formation-3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060423,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,36 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1070551</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.condition.always</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1070552</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.condition.primary-shocked</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1070408,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1194,6 +1194,141 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1080551</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.always</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1080552</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.restrained-target-exists</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1080407,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1080553</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.arm-overload-ready</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{"type":"Any","condition_ids":[1080558,1080559]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1080554</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.arm-overloaded</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080505}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1080555</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.beetle-role</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080506}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1080556</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.hound-role</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080507}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1080557</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.support-role-assigned</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{"type":"Any","condition_ids":[1080555,1080556]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1080558</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.arm-turn-overload-ready</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1081117,"comparison":"GreaterOrEqual","right_expression_id":1081115}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1080559</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.arm-hp-overload-ready</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1081102,"comparison":"Less","right_expression_id":1081118}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,21 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1094801</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.condition.always</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,6 +1344,21 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1104801</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.condition.always</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,6 +1359,21 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1114801</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.condition.always</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1374,6 +1374,21 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1124801</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.condition.always</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1389,6 +1389,21 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1134801</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.condition.always</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,6 +1404,21 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1144801</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.condition.always</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1419,6 +1419,21 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1154801</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.condition.always</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,6 +609,831 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980551</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.condition.always</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>980552</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.condition.no-branches</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":980406,"minimum_count":0,"maximum_count":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>990551</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.condition.always</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>990552</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.condition.current-subject-unshielded</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":991102,"comparison":"Equal","right_expression_id":991103}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1000551</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.condition.always</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1000552</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.condition.direwolf-coordinated</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1001108,"comparison":"Greater","right_expression_id":1001109}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1010551</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.condition.always</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1010552</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.condition.reset-sequence</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1011108,"comparison":"Greater","right_expression_id":1011107}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1010553</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.condition.needs-absorption</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1011109,"comparison":"Greater","right_expression_id":1011107}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.always</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1020562</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.core-wind</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020503}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1020563</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.core-lightning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020504}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1020564</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.core-imaginary</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020505}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020565</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.condition.no-flying-swords</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1020411,"minimum_count":0,"maximum_count":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1030561</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.condition.always</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1030562</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.condition.adjacent-frozen</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1030411,"minimum_count":1,"maximum_count":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1040561</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.condition.always</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1040562</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.condition.shielded</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1041103,"comparison":"Greater","right_expression_id":1041105}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1040563</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.condition.unshielded</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1041103,"comparison":"Equal","right_expression_id":1041105}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1050551</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.condition.always</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1050552</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.condition.reset</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1051108,"comparison":"Greater","right_expression_id":1051107}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.always</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1060552</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.sunset-ready</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1061117,"comparison":"GreaterOrEqual","right_expression_id":1061111}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060553</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.nightfall-second</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1061118,"comparison":"GreaterOrEqual","right_expression_id":1061111}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1060554</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.tomb-last</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1061119,"comparison":"LessOrEqual","right_expression_id":1061110}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1060555</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.tomb-more</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1061119,"comparison":"Greater","right_expression_id":1061110}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1060556</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.no-dreams</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060407,"minimum_count":0,"maximum_count":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1060557</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.sunset-not-ready</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{"type":"Not","condition_id":1060552}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1060558</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.nightfall-not-second</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{"type":"Not","condition_id":1060553}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1060560</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.primary-formation-0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060410,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1060561</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.primary-formation-1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060411,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1060562</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.primary-formation-2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060412,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1060563</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.primary-formation-3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060413,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1060570</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.current-formation-0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060420,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1060571</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.current-formation-1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060421,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1060572</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.current-formation-2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060422,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1060573</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.condition.current-formation-3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1060423,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1070551</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.condition.always</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1070552</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.condition.primary-shocked</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1070408,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1080551</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.always</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1080552</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.restrained-target-exists</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{"type":"SelectorCardinality","selector_id":1080407,"minimum_count":1,"maximum_count":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1080553</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.arm-overload-ready</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{"type":"Any","condition_ids":[1080558,1080559]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1080554</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.arm-overloaded</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080505}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1080555</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.beetle-role</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080506}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1080556</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.hound-role</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080507}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1080557</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.support-role-assigned</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{"type":"Any","condition_ids":[1080555,1080556]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1080558</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.arm-turn-overload-ready</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1081117,"comparison":"GreaterOrEqual","right_expression_id":1081115}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1080559</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.condition.arm-hp-overload-ready</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{"type":"Compare","left_expression_id":1081102,"comparison":"Less","right_expression_id":1081118}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1094801</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.condition.always</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1104801</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.condition.always</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1114801</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.condition.always</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1124801</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.condition.always</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1134801</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.condition.always</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1144801</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.condition.always</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1154801</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.condition.always</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{"type":"Constant","value":true}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ConditionExpression.xlsx
+++ b/config/data/ConditionExpression.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ConditionExpression" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConditionExpression" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,174 +499,185 @@
   </sheetPr>
   <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="12.7109375" customWidth="1" style="5" min="2" max="3"/>
+    <col width="30.7109375" customWidth="1" style="5" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>ConditionExpression</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>b577b9def34b94cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ff42256a38301ef9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>stable_key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>stable_key</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>i32</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>union&lt;ConditionExpressionNode&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>key;range=1..2147483647</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>length=1..160</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="D6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>1</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -595,8 +691,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>24201</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>24201</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -610,8 +708,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>980551</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>980551</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -625,8 +725,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>980552</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>980552</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -640,8 +742,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>990551</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>990551</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -655,8 +759,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>990552</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>990552</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -670,8 +776,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>1000551</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000551</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -685,8 +793,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>1000552</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1000552</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -700,8 +810,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>1010551</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1010551</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -715,8 +827,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>1010552</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1010552</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -730,8 +844,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>1010553</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1010553</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -745,12 +861,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>1020561</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1040561</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.condition.always</t>
+          <t>goal07.enemy.s07.condition.always</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -760,72 +878,82 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>1020562</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1040562</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.condition.core-wind</t>
+          <t>goal07.enemy.s07.condition.shielded</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020503}</t>
+          <t>{"type":"Compare","left_expression_id":1041103,"comparison":"Greater","right_expression_id":1041105}</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>1020563</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1040563</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.condition.core-lightning</t>
+          <t>goal07.enemy.s07.condition.unshielded</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020504}</t>
+          <t>{"type":"Compare","left_expression_id":1041103,"comparison":"Equal","right_expression_id":1041105}</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>1020564</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1050551</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.condition.core-imaginary</t>
+          <t>goal07.enemy.s08.condition.always</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020505}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>1020565</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1050552</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.condition.no-flying-swords</t>
+          <t>goal07.enemy.s08.condition.reset</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1020411,"minimum_count":0,"maximum_count":0}</t>
+          <t>{"type":"Compare","left_expression_id":1051108,"comparison":"Greater","right_expression_id":1051107}</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>1030561</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1060551</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>goal07.enemy.s06.condition.always</t>
+          <t>goal07.enemy.s09.condition.always</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -835,567 +963,631 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>1030562</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1060552</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>goal07.enemy.s06.condition.adjacent-frozen</t>
+          <t>goal07.enemy.s09.condition.sunset-ready</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1030411,"minimum_count":1,"maximum_count":2}</t>
+          <t>{"type":"Compare","left_expression_id":1061117,"comparison":"GreaterOrEqual","right_expression_id":1061111}</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>1040561</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1060553</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>goal07.enemy.s07.condition.always</t>
+          <t>goal07.enemy.s09.condition.nightfall-second</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"Compare","left_expression_id":1061118,"comparison":"GreaterOrEqual","right_expression_id":1061111}</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>1040562</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1060554</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>goal07.enemy.s07.condition.shielded</t>
+          <t>goal07.enemy.s09.condition.tomb-last</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1041103,"comparison":"Greater","right_expression_id":1041105}</t>
+          <t>{"type":"Compare","left_expression_id":1061119,"comparison":"LessOrEqual","right_expression_id":1061110}</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>1040563</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1060555</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>goal07.enemy.s07.condition.unshielded</t>
+          <t>goal07.enemy.s09.condition.tomb-more</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1041103,"comparison":"Equal","right_expression_id":1041105}</t>
+          <t>{"type":"Compare","left_expression_id":1061119,"comparison":"Greater","right_expression_id":1061110}</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>1050551</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1060556</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>goal07.enemy.s08.condition.always</t>
+          <t>goal07.enemy.s09.condition.no-dreams</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060407,"minimum_count":0,"maximum_count":0}</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>1050552</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1060557</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>goal07.enemy.s08.condition.reset</t>
+          <t>goal07.enemy.s09.condition.sunset-not-ready</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1051108,"comparison":"Greater","right_expression_id":1051107}</t>
+          <t>{"type":"Not","condition_id":1060552}</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>1060551</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1060558</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.always</t>
+          <t>goal07.enemy.s09.condition.nightfall-not-second</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"Not","condition_id":1060553}</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
-        <v>1060552</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1060560</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.sunset-ready</t>
+          <t>goal07.enemy.s09.condition.primary-formation-0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1061117,"comparison":"GreaterOrEqual","right_expression_id":1061111}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060410,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
-        <v>1060553</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1060561</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.nightfall-second</t>
+          <t>goal07.enemy.s09.condition.primary-formation-1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1061118,"comparison":"GreaterOrEqual","right_expression_id":1061111}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060411,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>1060554</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1060562</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.tomb-last</t>
+          <t>goal07.enemy.s09.condition.primary-formation-2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1061119,"comparison":"LessOrEqual","right_expression_id":1061110}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060412,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>1060555</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1060563</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.tomb-more</t>
+          <t>goal07.enemy.s09.condition.primary-formation-3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1061119,"comparison":"Greater","right_expression_id":1061110}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060413,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>1060556</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1060570</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.no-dreams</t>
+          <t>goal07.enemy.s09.condition.current-formation-0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060407,"minimum_count":0,"maximum_count":0}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060420,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
-        <v>1060557</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1060571</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.sunset-not-ready</t>
+          <t>goal07.enemy.s09.condition.current-formation-1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{"type":"Not","condition_id":1060552}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060421,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
-        <v>1060558</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1060572</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.nightfall-not-second</t>
+          <t>goal07.enemy.s09.condition.current-formation-2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{"type":"Not","condition_id":1060553}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060422,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
-        <v>1060560</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1060573</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.primary-formation-0</t>
+          <t>goal07.enemy.s09.condition.current-formation-3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060410,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1060423,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
-        <v>1060561</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1070551</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.primary-formation-1</t>
+          <t>goal07.enemy.s10.condition.always</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060411,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
-        <v>1060562</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1070552</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.primary-formation-2</t>
+          <t>goal07.enemy.s10.condition.primary-shocked</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060412,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1070408,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
-        <v>1060563</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1080551</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.primary-formation-3</t>
+          <t>goal07.enemy.s11.condition.always</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060413,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>1060570</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1080552</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.current-formation-0</t>
+          <t>goal07.enemy.s11.condition.restrained-target-exists</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060420,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1080407,"minimum_count":1,"maximum_count":1}</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
-        <v>1060571</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1080553</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.current-formation-1</t>
+          <t>goal07.enemy.s11.condition.arm-overload-ready</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060421,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"Any","condition_ids":[1080558,1080559]}</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>1060572</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1080554</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.current-formation-2</t>
+          <t>goal07.enemy.s11.condition.arm-overloaded</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060422,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080505}</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
-        <v>1060573</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1080555</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.condition.current-formation-3</t>
+          <t>goal07.enemy.s11.condition.beetle-role</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1060423,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080506}</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
-        <v>1070551</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1080556</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>goal07.enemy.s10.condition.always</t>
+          <t>goal07.enemy.s11.condition.hound-role</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080507}</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
-        <v>1070552</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1080557</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>goal07.enemy.s10.condition.primary-shocked</t>
+          <t>goal07.enemy.s11.condition.support-role-assigned</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1070408,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"Any","condition_ids":[1080555,1080556]}</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="n">
-        <v>1080551</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1080558</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.always</t>
+          <t>goal07.enemy.s11.condition.arm-turn-overload-ready</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"Compare","left_expression_id":1081117,"comparison":"GreaterOrEqual","right_expression_id":1081115}</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="n">
-        <v>1080552</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1080559</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.restrained-target-exists</t>
+          <t>goal07.enemy.s11.condition.arm-hp-overload-ready</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{"type":"SelectorCardinality","selector_id":1080407,"minimum_count":1,"maximum_count":1}</t>
+          <t>{"type":"Compare","left_expression_id":1081102,"comparison":"Less","right_expression_id":1081118}</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="n">
-        <v>1080553</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1094801</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.arm-overload-ready</t>
+          <t>goal07.enemy.s12.condition.always</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{"type":"Any","condition_ids":[1080558,1080559]}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="n">
-        <v>1080554</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1104801</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.arm-overloaded</t>
+          <t>goal07.enemy.s13.condition.always</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080505}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="n">
-        <v>1080555</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1114801</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.beetle-role</t>
+          <t>goal07.enemy.s14.condition.always</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080506}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="n">
-        <v>1080556</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1124801</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.hound-role</t>
+          <t>goal07.enemy.s15.condition.always</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{"type":"EffectExists","selector_id":1080401,"effect_id":1080507}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="n">
-        <v>1080557</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1134801</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.support-role-assigned</t>
+          <t>goal07.enemy.s16.condition.always</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{"type":"Any","condition_ids":[1080555,1080556]}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="n">
-        <v>1080558</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1154801</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.arm-turn-overload-ready</t>
+          <t>goal07.enemy.s18.condition.always</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1081117,"comparison":"GreaterOrEqual","right_expression_id":1081115}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1080559</v>
+        <v>1020561</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.condition.arm-hp-overload-ready</t>
+          <t>goal07.enemy.s05.condition.always</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{"type":"Compare","left_expression_id":1081102,"comparison":"Less","right_expression_id":1081118}</t>
+          <t>{"type":"Constant","value":true}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1094801</v>
+        <v>1020562</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>goal07.enemy.s12.condition.always</t>
+          <t>goal07.enemy.s05.condition.core-wind</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020503}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1104801</v>
+        <v>1020563</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>goal07.enemy.s13.condition.always</t>
+          <t>goal07.enemy.s05.condition.core-lightning</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020504}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1114801</v>
+        <v>1020564</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>goal07.enemy.s14.condition.always</t>
+          <t>goal07.enemy.s05.condition.core-imaginary</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"EffectExists","selector_id":1020404,"effect_id":1020505}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1124801</v>
+        <v>1020565</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>goal07.enemy.s15.condition.always</t>
+          <t>goal07.enemy.s05.condition.no-flying-swords</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1020411,"minimum_count":0,"maximum_count":0}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1134801</v>
+        <v>1144801</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>goal07.enemy.s16.condition.always</t>
+          <t>goal07.enemy.s17.condition.always</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1406,11 +1598,11 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1144801</v>
+        <v>1030561</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>goal07.enemy.s17.condition.always</t>
+          <t>goal07.enemy.s06.condition.always</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1421,20 +1613,26 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1154801</v>
+        <v>1030562</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>goal07.enemy.s18.condition.always</t>
+          <t>goal07.enemy.s06.condition.adjacent-frozen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{"type":"Constant","value":true}</t>
+          <t>{"type":"SelectorCardinality","selector_id":1030411,"minimum_count":1,"maximum_count":2}</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>